--- a/docs/zoho-creator/ZIA_REQUIREMENTS.xlsx
+++ b/docs/zoho-creator/ZIA_REQUIREMENTS.xlsx
@@ -435,7 +435,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Attach these requirement files to Zia: PRD PDF, BRD PDF, RFP PDF, PROCESS_DIAGRAMS PDF. If the dialog only accepts spreadsheets, upload this XLSX plus ZIA_UPLOAD.xlsx.</t>
+          <t>ONE FILE: upload ZIA_UPLOAD.pdf to Zia. It contains PRD + BRD + RFP + diagrams + fields + Deluge. This XLSX is only a spreadsheet fallback.</t>
         </is>
       </c>
     </row>
